--- a/files/excel-mastery-2-2.xlsx
+++ b/files/excel-mastery-2-2.xlsx
@@ -541,7 +541,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -549,8 +549,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="189">
+  <cellXfs count="191">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -647,9 +650,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -704,21 +704,12 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -731,29 +722,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
@@ -869,246 +839,290 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="25" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="25" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
     <cellStyle name="標準 2" xfId="2"/>
+    <cellStyle name="パーセント" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -1545,102 +1559,102 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I33"/>
+  <dimension ref="B2:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
-    <col width="2.36328125" customWidth="1" style="158" min="1" max="3"/>
-    <col width="10" customWidth="1" style="158" min="4" max="4"/>
-    <col width="22" customWidth="1" style="158" min="5" max="5"/>
-    <col width="14" customWidth="1" style="158" min="6" max="6"/>
-    <col width="24" customWidth="1" style="158" min="8" max="8"/>
-    <col width="14" customWidth="1" style="158" min="9" max="9"/>
+    <col width="2.36328125" customWidth="1" min="1" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.5" customHeight="1" s="158">
-      <c r="B2" s="75" t="inlineStr">
+    <row r="2" ht="19.5" customHeight="1">
+      <c r="B2" s="64" t="inlineStr">
         <is>
           <t>2-2. データ加工・クリーニング ― UNIQUE / FILTER / SORT</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1" s="158"/>
-    <row r="4" ht="13.5" customHeight="1" s="158">
+    <row r="3" ht="13.5" customHeight="1"/>
+    <row r="4" ht="13.5" customHeight="1">
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>元データの予約経路(OTA)には重複があります。動的配列関数でユニークな一覧を作ります。※Excelで開くと自動計算・spillします。</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="13.5" customHeight="1" s="158">
-      <c r="D5" s="77" t="inlineStr">
+    <row r="5" ht="13.5" customHeight="1">
+      <c r="D5" s="66" t="inlineStr">
         <is>
           <t>① 元データ：予約経路つき明細</t>
         </is>
       </c>
-      <c r="E5" s="78" t="n"/>
-      <c r="F5" s="78" t="n"/>
-      <c r="H5" s="111" t="inlineStr">
+      <c r="E5" s="67" t="n"/>
+      <c r="F5" s="67" t="n"/>
+      <c r="H5" s="97" t="inlineStr">
         <is>
           <t>② OTAのユニーク一覧</t>
         </is>
       </c>
-      <c r="I5" s="78" t="n"/>
-    </row>
-    <row r="6" ht="13.5" customHeight="1" s="158"/>
-    <row r="7" ht="13.5" customHeight="1" s="158">
-      <c r="D7" s="168" t="inlineStr">
+      <c r="I5" s="67" t="n"/>
+    </row>
+    <row r="6" ht="13.5" customHeight="1"/>
+    <row r="7" ht="13.5" customHeight="1">
+      <c r="D7" s="68" t="inlineStr">
         <is>
           <t>予約ID</t>
         </is>
       </c>
-      <c r="E7" s="168" t="inlineStr">
+      <c r="E7" s="68" t="inlineStr">
         <is>
           <t>予約経路(OTA)</t>
         </is>
       </c>
-      <c r="F7" s="168" t="inlineStr">
+      <c r="F7" s="68" t="inlineStr">
         <is>
           <t>売上(円)</t>
         </is>
       </c>
-      <c r="H7" s="168" t="inlineStr">
+      <c r="H7" s="68" t="inlineStr">
         <is>
           <t>数式</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="13.5" customHeight="1" s="158">
-      <c r="D8" s="80" t="inlineStr">
+    <row r="8" ht="13.5" customHeight="1">
+      <c r="D8" s="69" t="inlineStr">
         <is>
           <t>R001</t>
         </is>
       </c>
-      <c r="E8" s="80" t="inlineStr">
+      <c r="E8" s="69" t="inlineStr">
         <is>
           <t>楽天トラベル</t>
         </is>
       </c>
-      <c r="F8" s="81" t="n">
+      <c r="F8" s="70" t="n">
         <v>160000</v>
       </c>
-      <c r="H8" s="112" t="inlineStr">
+      <c r="H8" s="98" t="inlineStr">
         <is>
           <t>=SORT(UNIQUE(...))</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1" s="158">
-      <c r="D9" s="83" t="inlineStr">
+    <row r="9" ht="13.5" customHeight="1">
+      <c r="D9" s="72" t="inlineStr">
         <is>
           <t>R002</t>
         </is>
       </c>
-      <c r="E9" s="83" t="inlineStr">
+      <c r="E9" s="72" t="inlineStr">
         <is>
           <t>じゃらん</t>
         </is>
       </c>
-      <c r="F9" s="84" t="n">
+      <c r="F9" s="73" t="n">
         <v>108000</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1649,18 +1663,18 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="13.5" customHeight="1" s="158">
-      <c r="D10" s="83" t="inlineStr">
+    <row r="10" ht="13.5" customHeight="1">
+      <c r="D10" s="72" t="inlineStr">
         <is>
           <t>R003</t>
         </is>
       </c>
-      <c r="E10" s="83" t="inlineStr">
+      <c r="E10" s="72" t="inlineStr">
         <is>
           <t>Booking.com</t>
         </is>
       </c>
-      <c r="F10" s="84" t="n">
+      <c r="F10" s="73" t="n">
         <v>72000</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -1669,248 +1683,251 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="13.5" customHeight="1" s="158">
-      <c r="D11" s="83" t="inlineStr">
+    <row r="11" ht="13.5" customHeight="1">
+      <c r="D11" s="72" t="inlineStr">
         <is>
           <t>R004</t>
         </is>
       </c>
-      <c r="E11" s="83" t="inlineStr">
+      <c r="E11" s="72" t="inlineStr">
         <is>
           <t>楽天トラベル</t>
         </is>
       </c>
-      <c r="F11" s="84" t="n">
+      <c r="F11" s="73" t="n">
         <v>180000</v>
       </c>
     </row>
-    <row r="12" ht="13.5" customHeight="1" s="158">
-      <c r="D12" s="83" t="inlineStr">
+    <row r="12" ht="13.5" customHeight="1">
+      <c r="D12" s="72" t="inlineStr">
         <is>
           <t>R005</t>
         </is>
       </c>
-      <c r="E12" s="83" t="inlineStr">
+      <c r="E12" s="72" t="inlineStr">
         <is>
           <t>公式サイト</t>
         </is>
       </c>
-      <c r="F12" s="84" t="n">
+      <c r="F12" s="73" t="n">
         <v>95000</v>
       </c>
     </row>
-    <row r="13" ht="13.5" customHeight="1" s="158">
-      <c r="D13" s="83" t="inlineStr">
+    <row r="13" ht="13.5" customHeight="1">
+      <c r="D13" s="72" t="inlineStr">
         <is>
           <t>R006</t>
         </is>
       </c>
-      <c r="E13" s="83" t="inlineStr">
+      <c r="E13" s="72" t="inlineStr">
         <is>
           <t>じゃらん</t>
         </is>
       </c>
-      <c r="F13" s="84" t="n">
+      <c r="F13" s="73" t="n">
         <v>36000</v>
       </c>
     </row>
-    <row r="14" ht="13.5" customHeight="1" s="158">
-      <c r="D14" s="83" t="inlineStr">
+    <row r="14" ht="13.5" customHeight="1">
+      <c r="D14" s="72" t="inlineStr">
         <is>
           <t>R007</t>
         </is>
       </c>
-      <c r="E14" s="83" t="inlineStr">
+      <c r="E14" s="72" t="inlineStr">
         <is>
           <t>Expedia</t>
         </is>
       </c>
-      <c r="F14" s="84" t="n">
+      <c r="F14" s="73" t="n">
         <v>152000</v>
       </c>
-    </row>
-    <row r="15" ht="13.5" customHeight="1" s="158">
-      <c r="D15" s="83" t="inlineStr">
+      <c r="H14" s="97" t="inlineStr">
+        <is>
+          <t>③ 実例：OTA別の売上集計と FILTER 抽出</t>
+        </is>
+      </c>
+      <c r="I14" s="67" t="n"/>
+    </row>
+    <row r="15" ht="13.5" customHeight="1">
+      <c r="D15" s="72" t="inlineStr">
         <is>
           <t>R008</t>
         </is>
       </c>
-      <c r="E15" s="83" t="inlineStr">
+      <c r="E15" s="72" t="inlineStr">
         <is>
           <t>Booking.com</t>
         </is>
       </c>
-      <c r="F15" s="84" t="n">
+      <c r="F15" s="73" t="n">
         <v>74000</v>
       </c>
     </row>
-    <row r="16" ht="13.5" customHeight="1" s="158">
-      <c r="D16" s="83" t="inlineStr">
+    <row r="16" ht="13.5" customHeight="1">
+      <c r="D16" s="72" t="inlineStr">
         <is>
           <t>R009</t>
         </is>
       </c>
-      <c r="E16" s="83" t="inlineStr">
+      <c r="E16" s="72" t="inlineStr">
         <is>
           <t>楽天トラベル</t>
         </is>
       </c>
-      <c r="F16" s="84" t="n">
+      <c r="F16" s="73" t="n">
         <v>92000</v>
       </c>
-    </row>
-    <row r="17" ht="13.5" customHeight="1" s="158">
-      <c r="D17" s="83" t="inlineStr">
+      <c r="H16" s="68" t="inlineStr">
+        <is>
+          <t>OTA</t>
+        </is>
+      </c>
+      <c r="I16" s="68" t="inlineStr">
+        <is>
+          <t>売上計(円)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="13.5" customHeight="1">
+      <c r="D17" s="72" t="inlineStr">
         <is>
           <t>R010</t>
         </is>
       </c>
-      <c r="E17" s="83" t="inlineStr">
+      <c r="E17" s="72" t="inlineStr">
         <is>
           <t>公式サイト</t>
         </is>
       </c>
-      <c r="F17" s="84" t="n">
+      <c r="F17" s="73" t="n">
         <v>270000</v>
       </c>
-    </row>
-    <row r="18" ht="13.5" customHeight="1" s="158">
-      <c r="D18" s="83" t="inlineStr">
+      <c r="H17" s="69">
+        <f t="array" ref="H17:H22">_xlfn._xlws.SORT(_xlfn.UNIQUE(E8:E19))</f>
+        <v/>
+      </c>
+      <c r="I17" s="70">
+        <f t="array" ref="I17:I22">SUMIFS($F$8:$F$19,$E$8:$E$19,_xlfn.ANCHORARRAY(H17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="13.5" customHeight="1">
+      <c r="D18" s="72" t="inlineStr">
         <is>
           <t>R011</t>
         </is>
       </c>
-      <c r="E18" s="83" t="inlineStr">
+      <c r="E18" s="72" t="inlineStr">
         <is>
           <t>一休.com</t>
         </is>
       </c>
-      <c r="F18" s="84" t="n">
+      <c r="F18" s="73" t="n">
         <v>210000</v>
       </c>
-    </row>
-    <row r="19" ht="13.5" customHeight="1" s="158">
-      <c r="D19" s="83" t="inlineStr">
+      <c r="H18" s="72" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="I18" s="73" t="n">
+        <v>152000</v>
+      </c>
+    </row>
+    <row r="19" ht="13.5" customHeight="1">
+      <c r="D19" s="72" t="inlineStr">
         <is>
           <t>R012</t>
         </is>
       </c>
-      <c r="E19" s="83" t="inlineStr">
+      <c r="E19" s="72" t="inlineStr">
         <is>
           <t>じゃらん</t>
         </is>
       </c>
-      <c r="F19" s="84" t="n">
+      <c r="F19" s="73" t="n">
         <v>64000</v>
       </c>
-    </row>
-    <row r="20" ht="13.5" customHeight="1" s="158">
-      <c r="D20" s="83" t="n"/>
-      <c r="E20" s="113" t="inlineStr">
+      <c r="H19" s="72" t="inlineStr">
+        <is>
+          <t>じゃらん</t>
+        </is>
+      </c>
+      <c r="I19" s="73" t="n">
+        <v>208000</v>
+      </c>
+    </row>
+    <row r="20" ht="13.5" customHeight="1">
+      <c r="D20" s="72" t="n"/>
+      <c r="E20" s="99" t="inlineStr">
         <is>
           <t>・・・・</t>
         </is>
       </c>
-      <c r="F20" s="84" t="n"/>
-    </row>
-    <row r="21" ht="13.5" customHeight="1" s="158">
-      <c r="D21" s="83" t="n"/>
-      <c r="E21" s="83" t="n"/>
-      <c r="F21" s="84" t="n"/>
-    </row>
-    <row r="22" ht="13.5" customHeight="1" s="158">
-      <c r="H22" s="111" t="inlineStr">
-        <is>
-          <t>③ 実例：OTA別の売上集計と FILTER 抽出</t>
-        </is>
-      </c>
-      <c r="I22" s="78" t="n"/>
-    </row>
-    <row r="23" ht="13.5" customHeight="1" s="158"/>
-    <row r="24" ht="13.5" customHeight="1" s="158">
-      <c r="H24" s="168" t="inlineStr">
-        <is>
-          <t>OTA</t>
-        </is>
-      </c>
-      <c r="I24" s="168" t="inlineStr">
-        <is>
-          <t>売上計(円)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="13.5" customHeight="1" s="158">
-      <c r="H25" s="80">
-        <f t="array" ref="H25:H30">_xlfn._xlws.SORT(_xlfn.UNIQUE(E8:E19))</f>
-        <v/>
-      </c>
-      <c r="I25" s="81">
-        <f t="array" ref="I25:I30">SUMIFS($F$8:$F$19,$E$8:$E$19,_xlfn.ANCHORARRAY(H25))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="13.5" customHeight="1" s="158">
-      <c r="H26" s="83" t="inlineStr">
-        <is>
-          <t>Expedia</t>
-        </is>
-      </c>
-      <c r="I26" s="84" t="n">
-        <v>152000</v>
-      </c>
-    </row>
-    <row r="27" ht="13.5" customHeight="1" s="158">
-      <c r="H27" s="83" t="inlineStr">
-        <is>
-          <t>じゃらん</t>
-        </is>
-      </c>
-      <c r="I27" s="84" t="n">
-        <v>208000</v>
-      </c>
-    </row>
-    <row r="28" ht="13.5" customHeight="1" s="158">
-      <c r="H28" s="83" t="inlineStr">
+      <c r="F20" s="73" t="n"/>
+      <c r="H20" s="72" t="inlineStr">
         <is>
           <t>一休.com</t>
         </is>
       </c>
-      <c r="I28" s="84" t="n">
+      <c r="I20" s="73" t="n">
         <v>210000</v>
       </c>
     </row>
-    <row r="29" ht="13.5" customHeight="1" s="158">
-      <c r="H29" s="83" t="inlineStr">
+    <row r="21" ht="13.5" customHeight="1">
+      <c r="D21" s="72" t="n"/>
+      <c r="E21" s="72" t="n"/>
+      <c r="F21" s="73" t="n"/>
+      <c r="H21" s="72" t="inlineStr">
         <is>
           <t>楽天トラベル</t>
         </is>
       </c>
-      <c r="I29" s="84" t="n">
+      <c r="I21" s="73" t="n">
         <v>432000</v>
       </c>
     </row>
-    <row r="30" ht="13.5" customHeight="1" s="158">
-      <c r="H30" s="83" t="inlineStr">
+    <row r="22" ht="13.5" customHeight="1">
+      <c r="D22" s="72" t="n"/>
+      <c r="E22" s="72" t="n"/>
+      <c r="F22" s="73" t="n"/>
+      <c r="H22" s="72" t="inlineStr">
         <is>
           <t>公式サイト</t>
         </is>
       </c>
-      <c r="I30" s="84" t="n">
+      <c r="I22" s="73" t="n">
         <v>365000</v>
       </c>
     </row>
-    <row r="31" ht="13.5" customHeight="1" s="158">
-      <c r="H31" s="83" t="n"/>
-      <c r="I31" s="84" t="n"/>
-    </row>
-    <row r="32" ht="13.5" customHeight="1" s="158">
-      <c r="H32" s="83" t="n"/>
-      <c r="I32" s="84" t="n"/>
-    </row>
-    <row r="33" ht="13.5" customHeight="1" s="158">
-      <c r="H33" s="83" t="n"/>
-      <c r="I33" s="84" t="n"/>
-    </row>
+    <row r="23" ht="13.5" customHeight="1">
+      <c r="D23" s="72" t="n"/>
+      <c r="E23" s="72" t="n"/>
+      <c r="F23" s="73" t="n"/>
+      <c r="H23" s="72" t="n"/>
+      <c r="I23" s="73" t="n"/>
+    </row>
+    <row r="24" ht="13.5" customHeight="1">
+      <c r="D24" s="72" t="n"/>
+      <c r="E24" s="72" t="n"/>
+      <c r="F24" s="73" t="n"/>
+      <c r="H24" s="72" t="n"/>
+      <c r="I24" s="73" t="n"/>
+    </row>
+    <row r="25" ht="13.5" customHeight="1">
+      <c r="D25" s="72" t="n"/>
+      <c r="E25" s="72" t="n"/>
+      <c r="F25" s="73" t="n"/>
+      <c r="H25" s="72" t="n"/>
+      <c r="I25" s="73" t="n"/>
+    </row>
+    <row r="26" ht="13.5" customHeight="1"/>
+    <row r="27" ht="13.5" customHeight="1"/>
+    <row r="28" ht="13.5" customHeight="1"/>
+    <row r="29" ht="13.5" customHeight="1"/>
+    <row r="30" ht="13.5" customHeight="1"/>
+    <row r="31" ht="13.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/files/excel-mastery-2-2.xlsx
+++ b/files/excel-mastery-2-2.xlsx
@@ -3,10 +3,10 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-1605" yWindow="-16320" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="280" windowWidth="17320" windowHeight="10400" tabRatio="773" firstSheet="2" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2-2_クリーニング" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2-2_クリーニング_スピル関数" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -553,7 +553,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1049,74 +1049,77 @@
     <xf numFmtId="3" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1559,15 +1562,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I25"/>
+  <dimension ref="B2:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="2.36328125" customWidth="1" min="1" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="6" max="7"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="2" ht="19.5" customHeight="1">
@@ -1593,12 +1596,13 @@
       </c>
       <c r="E5" s="67" t="n"/>
       <c r="F5" s="67" t="n"/>
-      <c r="H5" s="97" t="inlineStr">
+      <c r="G5" s="67" t="n"/>
+      <c r="I5" s="97" t="inlineStr">
         <is>
           <t>② OTAのユニーク一覧</t>
         </is>
       </c>
-      <c r="I5" s="67" t="n"/>
+      <c r="J5" s="67" t="n"/>
     </row>
     <row r="6" ht="13.5" customHeight="1"/>
     <row r="7" ht="13.5" customHeight="1">
@@ -1612,12 +1616,17 @@
           <t>予約経路(OTA)</t>
         </is>
       </c>
-      <c r="F7" s="68" t="inlineStr">
+      <c r="F7" s="138" t="inlineStr">
+        <is>
+          <t>海外/国内</t>
+        </is>
+      </c>
+      <c r="G7" s="68" t="inlineStr">
         <is>
           <t>売上(円)</t>
         </is>
       </c>
-      <c r="H7" s="68" t="inlineStr">
+      <c r="I7" s="68" t="inlineStr">
         <is>
           <t>数式</t>
         </is>
@@ -1634,14 +1643,20 @@
           <t>楽天トラベル</t>
         </is>
       </c>
-      <c r="F8" s="70" t="n">
+      <c r="F8" s="102" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="G8" s="70" t="n">
         <v>160000</v>
       </c>
-      <c r="H8" s="98" t="inlineStr">
-        <is>
-          <t>=SORT(UNIQUE(...))</t>
-        </is>
-      </c>
+      <c r="I8" s="98" t="inlineStr">
+        <is>
+          <t>=SORT(UNIQUE(FILTER(#:#,#:#=***)))</t>
+        </is>
+      </c>
+      <c r="J8" s="98" t="n"/>
     </row>
     <row r="9" ht="13.5" customHeight="1">
       <c r="D9" s="72" t="inlineStr">
@@ -1654,10 +1669,15 @@
           <t>じゃらん</t>
         </is>
       </c>
-      <c r="F9" s="73" t="n">
+      <c r="F9" s="72" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="G9" s="73" t="n">
         <v>108000</v>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>↑ このセルに1つ入れるだけで、</t>
         </is>
@@ -1674,10 +1694,15 @@
           <t>Booking.com</t>
         </is>
       </c>
-      <c r="F10" s="73" t="n">
+      <c r="F10" s="99" t="inlineStr">
+        <is>
+          <t>海外</t>
+        </is>
+      </c>
+      <c r="G10" s="73" t="n">
         <v>72000</v>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>重複を除いた経路名が下方向にスピル表示されます。</t>
         </is>
@@ -1694,9 +1719,15 @@
           <t>楽天トラベル</t>
         </is>
       </c>
-      <c r="F11" s="73" t="n">
+      <c r="F11" s="72" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="G11" s="73" t="n">
         <v>180000</v>
       </c>
+      <c r="I11" s="188" t="n"/>
     </row>
     <row r="12" ht="13.5" customHeight="1">
       <c r="D12" s="72" t="inlineStr">
@@ -1709,7 +1740,12 @@
           <t>公式サイト</t>
         </is>
       </c>
-      <c r="F12" s="73" t="n">
+      <c r="F12" s="72" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="G12" s="73" t="n">
         <v>95000</v>
       </c>
     </row>
@@ -1724,7 +1760,12 @@
           <t>じゃらん</t>
         </is>
       </c>
-      <c r="F13" s="73" t="n">
+      <c r="F13" s="72" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="G13" s="73" t="n">
         <v>36000</v>
       </c>
     </row>
@@ -1739,15 +1780,20 @@
           <t>Expedia</t>
         </is>
       </c>
-      <c r="F14" s="73" t="n">
+      <c r="F14" s="99" t="inlineStr">
+        <is>
+          <t>海外</t>
+        </is>
+      </c>
+      <c r="G14" s="73" t="n">
         <v>152000</v>
       </c>
-      <c r="H14" s="97" t="inlineStr">
+      <c r="I14" s="97" t="inlineStr">
         <is>
           <t>③ 実例：OTA別の売上集計と FILTER 抽出</t>
         </is>
       </c>
-      <c r="I14" s="67" t="n"/>
+      <c r="J14" s="67" t="n"/>
     </row>
     <row r="15" ht="13.5" customHeight="1">
       <c r="D15" s="72" t="inlineStr">
@@ -1760,7 +1806,12 @@
           <t>Booking.com</t>
         </is>
       </c>
-      <c r="F15" s="73" t="n">
+      <c r="F15" s="99" t="inlineStr">
+        <is>
+          <t>海外</t>
+        </is>
+      </c>
+      <c r="G15" s="73" t="n">
         <v>74000</v>
       </c>
     </row>
@@ -1775,15 +1826,20 @@
           <t>楽天トラベル</t>
         </is>
       </c>
-      <c r="F16" s="73" t="n">
+      <c r="F16" s="72" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="G16" s="73" t="n">
         <v>92000</v>
       </c>
-      <c r="H16" s="68" t="inlineStr">
+      <c r="I16" s="68" t="inlineStr">
         <is>
           <t>OTA</t>
         </is>
       </c>
-      <c r="I16" s="68" t="inlineStr">
+      <c r="J16" s="68" t="inlineStr">
         <is>
           <t>売上計(円)</t>
         </is>
@@ -1800,15 +1856,20 @@
           <t>公式サイト</t>
         </is>
       </c>
-      <c r="F17" s="73" t="n">
+      <c r="F17" s="72" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="G17" s="73" t="n">
         <v>270000</v>
       </c>
-      <c r="H17" s="69">
-        <f t="array" ref="H17:H22">_xlfn._xlws.SORT(_xlfn.UNIQUE(E8:E19))</f>
+      <c r="I17" s="69">
+        <f t="array" ref="I17:I20">_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(E8:E19, F8:F19="国内")))</f>
         <v/>
       </c>
-      <c r="I17" s="70">
-        <f t="array" ref="I17:I22">SUMIFS($F$8:$F$19,$E$8:$E$19,_xlfn.ANCHORARRAY(H17))</f>
+      <c r="J17" s="70">
+        <f t="array" ref="J17:J20">SUMIFS($G$8:$G$19,$E$8:$E$19,_xlfn.ANCHORARRAY(I17))</f>
         <v/>
       </c>
     </row>
@@ -1823,16 +1884,21 @@
           <t>一休.com</t>
         </is>
       </c>
-      <c r="F18" s="73" t="n">
+      <c r="F18" s="72" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="G18" s="73" t="n">
         <v>210000</v>
       </c>
-      <c r="H18" s="72" t="inlineStr">
-        <is>
-          <t>Expedia</t>
-        </is>
-      </c>
-      <c r="I18" s="73" t="n">
-        <v>152000</v>
+      <c r="I18" s="72" t="inlineStr">
+        <is>
+          <t>一休.com</t>
+        </is>
+      </c>
+      <c r="J18" s="73" t="n">
+        <v>210000</v>
       </c>
     </row>
     <row r="19" ht="13.5" customHeight="1">
@@ -1846,16 +1912,21 @@
           <t>じゃらん</t>
         </is>
       </c>
-      <c r="F19" s="73" t="n">
+      <c r="F19" s="72" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="G19" s="73" t="n">
         <v>64000</v>
       </c>
-      <c r="H19" s="72" t="inlineStr">
-        <is>
-          <t>じゃらん</t>
-        </is>
-      </c>
-      <c r="I19" s="73" t="n">
-        <v>208000</v>
+      <c r="I19" s="72" t="inlineStr">
+        <is>
+          <t>楽天トラベル</t>
+        </is>
+      </c>
+      <c r="J19" s="73" t="n">
+        <v>432000</v>
       </c>
     </row>
     <row r="20" ht="13.5" customHeight="1">
@@ -1865,62 +1936,56 @@
           <t>・・・・</t>
         </is>
       </c>
-      <c r="F20" s="73" t="n"/>
-      <c r="H20" s="72" t="inlineStr">
-        <is>
-          <t>一休.com</t>
-        </is>
-      </c>
-      <c r="I20" s="73" t="n">
-        <v>210000</v>
+      <c r="F20" s="99" t="n"/>
+      <c r="G20" s="73" t="n"/>
+      <c r="I20" s="72" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="J20" s="73" t="n">
+        <v>365000</v>
       </c>
     </row>
     <row r="21" ht="13.5" customHeight="1">
       <c r="D21" s="72" t="n"/>
       <c r="E21" s="72" t="n"/>
-      <c r="F21" s="73" t="n"/>
-      <c r="H21" s="72" t="inlineStr">
-        <is>
-          <t>楽天トラベル</t>
-        </is>
-      </c>
-      <c r="I21" s="73" t="n">
-        <v>432000</v>
-      </c>
+      <c r="F21" s="72" t="n"/>
+      <c r="G21" s="73" t="n"/>
+      <c r="I21" s="72" t="n"/>
+      <c r="J21" s="73" t="n"/>
     </row>
     <row r="22" ht="13.5" customHeight="1">
       <c r="D22" s="72" t="n"/>
       <c r="E22" s="72" t="n"/>
-      <c r="F22" s="73" t="n"/>
-      <c r="H22" s="72" t="inlineStr">
-        <is>
-          <t>公式サイト</t>
-        </is>
-      </c>
-      <c r="I22" s="73" t="n">
-        <v>365000</v>
-      </c>
+      <c r="F22" s="72" t="n"/>
+      <c r="G22" s="73" t="n"/>
+      <c r="I22" s="72" t="n"/>
+      <c r="J22" s="73" t="n"/>
     </row>
     <row r="23" ht="13.5" customHeight="1">
       <c r="D23" s="72" t="n"/>
       <c r="E23" s="72" t="n"/>
-      <c r="F23" s="73" t="n"/>
-      <c r="H23" s="72" t="n"/>
-      <c r="I23" s="73" t="n"/>
+      <c r="F23" s="72" t="n"/>
+      <c r="G23" s="73" t="n"/>
+      <c r="I23" s="72" t="n"/>
+      <c r="J23" s="73" t="n"/>
     </row>
     <row r="24" ht="13.5" customHeight="1">
       <c r="D24" s="72" t="n"/>
       <c r="E24" s="72" t="n"/>
-      <c r="F24" s="73" t="n"/>
-      <c r="H24" s="72" t="n"/>
-      <c r="I24" s="73" t="n"/>
+      <c r="F24" s="72" t="n"/>
+      <c r="G24" s="73" t="n"/>
+      <c r="I24" s="72" t="n"/>
+      <c r="J24" s="73" t="n"/>
     </row>
     <row r="25" ht="13.5" customHeight="1">
       <c r="D25" s="72" t="n"/>
       <c r="E25" s="72" t="n"/>
-      <c r="F25" s="73" t="n"/>
-      <c r="H25" s="72" t="n"/>
-      <c r="I25" s="73" t="n"/>
+      <c r="F25" s="72" t="n"/>
+      <c r="G25" s="73" t="n"/>
+      <c r="I25" s="72" t="n"/>
+      <c r="J25" s="73" t="n"/>
     </row>
     <row r="26" ht="13.5" customHeight="1"/>
     <row r="27" ht="13.5" customHeight="1"/>
